--- a/data/trans_camb/P16A06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A06-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,37</t>
+          <t>-1,76; 2,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,03</t>
+          <t>-1,36; 2,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,56</t>
+          <t>0,81; 5,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,68</t>
+          <t>-2,22; 4,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,88</t>
+          <t>-2,44; 2,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,46</t>
+          <t>0,05; 5,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,3</t>
+          <t>-1,26; 2,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,25</t>
+          <t>-1,07; 2,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,78</t>
+          <t>1,18; 4,77</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-69,68; 206,25</t>
+          <t>-67,4; 210,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,43; 237,96</t>
+          <t>-50,83; 257,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,04; 523,74</t>
+          <t>17,1; 470,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,45; 235,3</t>
+          <t>-53,99; 245,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,72; 187,15</t>
+          <t>-60,09; 182,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 366,83</t>
+          <t>-4,31; 333,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,68; 139,57</t>
+          <t>-42,8; 133,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 142,49</t>
+          <t>-36,7; 117,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,74; 273,82</t>
+          <t>31,69; 313,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,79</t>
+          <t>-1,93; 2,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,17</t>
+          <t>-1,86; 2,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,65</t>
+          <t>0,02; 4,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,2</t>
+          <t>-1,9; 2,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,94</t>
+          <t>-0,9; 4,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,66</t>
+          <t>3,34; 8,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,93</t>
+          <t>-1,45; 1,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,23</t>
+          <t>-1,12; 2,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,76</t>
+          <t>2,38; 5,91</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-71,28; 306,23</t>
+          <t>-72,81; 326,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,75; 207,81</t>
+          <t>-68,79; 345,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 458,73</t>
+          <t>-11,14; 544,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-70,3; 231,58</t>
+          <t>-67,57; 265,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,78; 366,56</t>
+          <t>-42,54; 374,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,3; 814,22</t>
+          <t>77,3; 833,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,43; 172,69</t>
+          <t>-54,94; 161,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 155,47</t>
+          <t>-40,96; 186,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61,55; 460,42</t>
+          <t>76,58; 510,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,53</t>
+          <t>-0,05; 3,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,66</t>
+          <t>-0,56; 2,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 5,31</t>
+          <t>-1,06; 5,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 4,92</t>
+          <t>-3,4; 4,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 10,97</t>
+          <t>-0,73; 10,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 13,59</t>
+          <t>3,24; 13,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,19</t>
+          <t>-0,02; 3,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,87</t>
+          <t>0,17; 3,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 6,56</t>
+          <t>-0,2; 6,27</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 461,9</t>
+          <t>-9,11; 425,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,5; 337,83</t>
+          <t>-32,69; 287,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 542,59</t>
+          <t>-37,07; 477,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,28; 320,99</t>
+          <t>-58,58; 236,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 561,16</t>
+          <t>-19,5; 450,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,97; 744,35</t>
+          <t>34,53; 590,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 234,25</t>
+          <t>-6,23; 222,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 280,64</t>
+          <t>-0,34; 272,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,72; 385,7</t>
+          <t>-1,28; 371,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,32</t>
+          <t>-1,86; 0,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,2</t>
+          <t>-0,46; 2,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,08</t>
+          <t>2,12; 5,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,96</t>
+          <t>-1,09; 3,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,26</t>
+          <t>0,07; 4,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,71</t>
+          <t>-1,34; 4,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,99</t>
+          <t>-1,09; 1,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,6</t>
+          <t>0,13; 2,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,42</t>
+          <t>1,21; 4,51</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,18; 18,9</t>
+          <t>-62,18; 28,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 130,12</t>
+          <t>-17,6; 122,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68,01; 276,63</t>
+          <t>67,55; 286,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 126,48</t>
+          <t>-25,66; 135,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 183,22</t>
+          <t>-1,68; 170,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 168,67</t>
+          <t>-28,21; 166,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,21; 43,0</t>
+          <t>-34,08; 48,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,27; 112,21</t>
+          <t>5,14; 112,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>41,22; 192,79</t>
+          <t>42,13; 192,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,22</t>
+          <t>-3,13; 1,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,23</t>
+          <t>-2,43; 2,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,5</t>
+          <t>-0,13; 5,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,32</t>
+          <t>2,43; 7,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,15</t>
+          <t>3,51; 9,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,39; 13,73</t>
+          <t>6,93; 14,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,43</t>
+          <t>0,69; 4,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,13</t>
+          <t>1,41; 5,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,97</t>
+          <t>5,19; 10,03</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-74,12; 75,72</t>
+          <t>-71,56; 106,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,0; 141,75</t>
+          <t>-49,96; 140,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 347,05</t>
+          <t>-7,6; 306,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39,58; 298,46</t>
+          <t>49,22; 298,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>60,56; 363,32</t>
+          <t>69,55; 397,02</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>133,06; 557,93</t>
+          <t>148,84; 567,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,72; 175,18</t>
+          <t>12,55; 165,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>33,96; 212,63</t>
+          <t>28,11; 200,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>118,96; 384,86</t>
+          <t>118,93; 396,69</t>
         </is>
       </c>
     </row>
@@ -1762,42 +1762,42 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,24</t>
+          <t>1,24; 9,62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,1</t>
+          <t>0,66; 5,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,93</t>
+          <t>2,08; 6,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,65; 9,29</t>
+          <t>4,89; 9,6</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,1</t>
+          <t>0,58; 3,99</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,6</t>
+          <t>1,65; 5,48</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,01</t>
+          <t>3,96; 8,11</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9,25; 103,64</t>
+          <t>9,16; 98,87</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30,8; 144,47</t>
+          <t>30,34; 134,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>70,47; 195,96</t>
+          <t>71,64; 191,79</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,83; 103,57</t>
+          <t>10,82; 103,21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>28,78; 139,2</t>
+          <t>29,34; 137,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>71,45; 203,13</t>
+          <t>70,74; 208,78</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,72</t>
+          <t>-0,72; 0,69</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,48</t>
+          <t>-0,1; 1,4</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,88</t>
+          <t>1,68; 3,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,25</t>
+          <t>1,13; 3,19</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,47</t>
+          <t>2,26; 4,6</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,06</t>
+          <t>3,79; 7,04</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,72</t>
+          <t>0,44; 1,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,8</t>
+          <t>1,4; 2,81</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,28</t>
+          <t>3,31; 5,21</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 43,31</t>
+          <t>-30,53; 41,09</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 90,41</t>
+          <t>-4,55; 87,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>77,86; 238,21</t>
+          <t>78,07; 243,22</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19,48; 87,92</t>
+          <t>24,17; 85,85</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>46,26; 122,51</t>
+          <t>47,95; 125,61</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>83,68; 191,49</t>
+          <t>84,1; 188,59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,93; 61,75</t>
+          <t>13,48; 63,49</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>39,46; 100,68</t>
+          <t>41,24; 100,47</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>96,93; 192,7</t>
+          <t>101,94; 187,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A06-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>2,88</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,34</t>
+          <t>-1,7; 2,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,8</t>
+          <t>-1,25; 2,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,56</t>
+          <t>0,66; 4,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,05</t>
+          <t>-2,16; 4,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,86</t>
+          <t>-2,72; 2,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,21</t>
+          <t>-0,27; 5,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,13</t>
+          <t>-1,13; 2,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,06</t>
+          <t>-1,18; 2,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,77</t>
+          <t>1,28; 4,61</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>153,96%</t>
+          <t>141,13%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>124,52%</t>
+          <t>118,81%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-67,4; 210,45</t>
+          <t>-68,29; 174,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,83; 257,94</t>
+          <t>-51,34; 245,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,1; 470,19</t>
+          <t>5,26; 401,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,99; 245,48</t>
+          <t>-52,39; 247,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,09; 182,4</t>
+          <t>-63,02; 178,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 333,55</t>
+          <t>-9,07; 321,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,8; 133,46</t>
+          <t>-39,88; 127,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,7; 117,19</t>
+          <t>-38,01; 126,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,69; 313,15</t>
+          <t>31,84; 265,25</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>3,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,73</t>
+          <t>-1,96; 2,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,42</t>
+          <t>-2,13; 2,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,95</t>
+          <t>-0,37; 4,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,23</t>
+          <t>-2,03; 2,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,01</t>
+          <t>-1,05; 3,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,56</t>
+          <t>3,28; 8,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,88</t>
+          <t>-1,27; 1,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,15</t>
+          <t>-0,79; 2,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,91</t>
+          <t>2,23; 5,82</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111,96%</t>
+          <t>105,05%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>301,7%</t>
+          <t>300,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>198,56%</t>
+          <t>196,09%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,81; 326,22</t>
+          <t>-65,29; 348,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,79; 345,01</t>
+          <t>-72,23; 256,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 544,25</t>
+          <t>-21,71; 437,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,57; 265,53</t>
+          <t>-76,78; 202,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 374,71</t>
+          <t>-41,85; 360,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,3; 833,0</t>
+          <t>85,47; 855,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 161,2</t>
+          <t>-49,67; 159,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,96; 186,1</t>
+          <t>-31,21; 191,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76,58; 510,15</t>
+          <t>65,17; 481,0</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,33</t>
+          <t>7,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>5,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,55</t>
+          <t>0,09; 3,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,5</t>
+          <t>-0,59; 2,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 5,11</t>
+          <t>2,36; 7,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 4,68</t>
+          <t>-3,03; 4,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 10,28</t>
+          <t>-0,16; 10,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 13,16</t>
+          <t>3,53; 12,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,17</t>
+          <t>0,03; 3,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,88</t>
+          <t>0,31; 3,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 6,27</t>
+          <t>3,69; 7,83</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>160,34%</t>
+          <t>305,68%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>208,44%</t>
+          <t>198,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>167,27%</t>
+          <t>270,27%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 425,9</t>
+          <t>-6,76; 397,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,69; 287,31</t>
+          <t>-34,02; 341,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 477,1</t>
+          <t>93,83; 872,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 236,79</t>
+          <t>-51,12; 224,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 450,11</t>
+          <t>-24,66; 469,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,53; 590,06</t>
+          <t>37,94; 674,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 222,08</t>
+          <t>-2,37; 241,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 272,21</t>
+          <t>6,61; 282,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 371,56</t>
+          <t>120,97; 562,36</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>3,53</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,47</t>
+          <t>-1,98; 0,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,22</t>
+          <t>-0,63; 2,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,25</t>
+          <t>1,99; 5,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,04</t>
+          <t>-1,28; 2,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,3</t>
+          <t>0,11; 4,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,56</t>
+          <t>1,72; 5,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,08</t>
+          <t>-1,15; 0,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,42</t>
+          <t>0,26; 2,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,51</t>
+          <t>2,6; 4,96</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>148,12%</t>
+          <t>146,21%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>111,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>112,79%</t>
+          <t>133,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,18; 28,7</t>
+          <t>-67,31; 17,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 122,9</t>
+          <t>-22,12; 121,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67,55; 286,44</t>
+          <t>62,75; 268,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 135,11</t>
+          <t>-29,91; 108,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 170,91</t>
+          <t>-0,69; 155,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,21; 166,74</t>
+          <t>36,49; 236,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 48,27</t>
+          <t>-35,9; 41,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,14; 112,44</t>
+          <t>7,09; 113,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,13; 192,86</t>
+          <t>76,58; 231,06</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,72</t>
+          <t>11,49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,84</t>
+          <t>7,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,31</t>
+          <t>-3,07; 1,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,32</t>
+          <t>-2,75; 2,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,24</t>
+          <t>-0,56; 4,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,48</t>
+          <t>2,33; 7,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,21</t>
+          <t>3,51; 9,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,93; 14,13</t>
+          <t>8,95; 13,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,33</t>
+          <t>0,98; 4,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,18</t>
+          <t>1,4; 5,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,19; 10,03</t>
+          <t>5,84; 9,55</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>289,37%</t>
+          <t>310,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>229,47%</t>
+          <t>226,8%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,56; 106,31</t>
+          <t>-71,2; 83,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,96; 140,56</t>
+          <t>-59,36; 118,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 306,69</t>
+          <t>-18,44; 243,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49,22; 298,86</t>
+          <t>37,36; 290,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>69,55; 397,02</t>
+          <t>61,6; 364,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>148,84; 567,0</t>
+          <t>169,65; 570,2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,55; 165,05</t>
+          <t>20,19; 171,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>28,11; 200,2</t>
+          <t>30,56; 201,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>118,93; 396,69</t>
+          <t>126,04; 367,31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>6,9</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>6,07</t>
         </is>
       </c>
     </row>
@@ -1762,42 +1762,42 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,24; 9,62</t>
+          <t>1,62; 9,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,0</t>
+          <t>0,68; 5,26</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,65</t>
+          <t>2,24; 6,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,6</t>
+          <t>4,71; 9,17</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,99</t>
+          <t>0,41; 4,09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,48</t>
+          <t>1,76; 5,61</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,11</t>
+          <t>3,9; 7,97</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>123,59%</t>
+          <t>119,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>127,81%</t>
+          <t>130,59%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9,16; 98,87</t>
+          <t>9,15; 107,05</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30,34; 134,19</t>
+          <t>32,6; 138,33</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>71,64; 191,79</t>
+          <t>69,65; 189,63</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,82; 103,21</t>
+          <t>7,64; 105,8</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>29,34; 137,95</t>
+          <t>29,5; 145,15</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70,74; 208,78</t>
+          <t>69,58; 204,27</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>6,27</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>4,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,69</t>
+          <t>-0,73; 0,73</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,4</t>
+          <t>-0,06; 1,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,97</t>
+          <t>2,37; 4,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,19</t>
+          <t>1,14; 3,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,6</t>
+          <t>2,23; 4,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,04</t>
+          <t>5,15; 7,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,75</t>
+          <t>0,39; 1,72</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,81</t>
+          <t>1,37; 2,81</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,21</t>
+          <t>4,15; 5,48</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>149,1%</t>
+          <t>163,89%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>137,0%</t>
+          <t>150,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>141,79%</t>
+          <t>155,69%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 41,09</t>
+          <t>-30,47; 46,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 87,73</t>
+          <t>-3,22; 79,38</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>78,07; 243,22</t>
+          <t>99,58; 245,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24,17; 85,85</t>
+          <t>24,34; 92,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>47,95; 125,61</t>
+          <t>47,82; 123,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>84,1; 188,59</t>
+          <t>110,33; 199,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,48; 63,49</t>
+          <t>11,17; 61,9</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>41,24; 100,47</t>
+          <t>39,52; 100,29</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>101,94; 187,1</t>
+          <t>120,54; 195,26</t>
         </is>
       </c>
     </row>
